--- a/data/trans_orig/IP07C10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C10-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2007 (tasa de respuesta: 88,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14126</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20008</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32402</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36620</t>
+          <t>37886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53804</t>
+          <t>55033</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,29%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18409</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30745</t>
+          <t>31303</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>32325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42779</t>
+          <t>41994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>60118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10258</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21915</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20151</t>
+          <t>20340</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>34314</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29210</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43430</t>
+          <t>43587</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31312</t>
+          <t>31807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>46377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>64222</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84973</t>
+          <t>85284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,5%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36811</t>
+          <t>37039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51795</t>
+          <t>51961</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43002</t>
+          <t>43244</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68561</t>
+          <t>69033</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89787</t>
+          <t>91060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,58%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10473</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21606</t>
+          <t>22095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22023</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24377</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39929</t>
+          <t>40814</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30783</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13692</t>
+          <t>14230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>25545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36464</t>
+          <t>35455</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52415</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14633</t>
+          <t>14521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25536</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18391</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36380</t>
+          <t>35884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52685</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>44,61%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6705</t>
+          <t>6862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15583</t>
+          <t>15710</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11344</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>20778</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>34316</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,46%</t>
         </is>
       </c>
     </row>
@@ -2470,47 +2470,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6116</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5524</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2081</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>21341</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>26909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41826</t>
+          <t>41448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51917</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73836</t>
+          <t>73749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,68%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28016</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43244</t>
+          <t>44059</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30774</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62525</t>
+          <t>64064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>85126</t>
+          <t>84903</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>51,43%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18371</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15184</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>29999</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4218</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8751</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5821</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>95089</t>
+          <t>95716</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>121379</t>
+          <t>121488</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>104230</t>
+          <t>103230</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>130739</t>
+          <t>130986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>205767</t>
+          <t>206096</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>245515</t>
+          <t>245856</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112446</t>
+          <t>112991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>139213</t>
+          <t>139275</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110160</t>
+          <t>109087</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>137218</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>231285</t>
+          <t>228288</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>267085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,02%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37943</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>57987</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>49995</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>71300</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>91711</t>
+          <t>92263</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>123115</t>
+          <t>123741</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6977</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4660</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14568</t>
+          <t>14564</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6498</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>733</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6347</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2012 (tasa de respuesta: 91,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>17699</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31314</t>
+          <t>30910</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18941</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32664</t>
+          <t>32548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40523</t>
+          <t>40205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60008</t>
+          <t>58745</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35037</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31328</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45070</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56708</t>
+          <t>57388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76300</t>
+          <t>76226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14279</t>
+          <t>14393</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21127</t>
+          <t>21357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>27998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43426</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>31771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46586</t>
+          <t>46666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64798</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>86669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51160</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28231</t>
+          <t>28514</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43385</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68435</t>
+          <t>67582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90131</t>
+          <t>88389</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8607</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19449</t>
+          <t>20340</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13740</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25740</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40836</t>
+          <t>41087</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>14379</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26739</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>26061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43992</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62227</t>
+          <t>61590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,95%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>27065</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>39263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19395</t>
+          <t>19400</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31356</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48636</t>
+          <t>49159</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67340</t>
+          <t>66707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>51,93%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5303</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>14491</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23189</t>
+          <t>22787</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32725</t>
+          <t>32391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17992</t>
+          <t>17791</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32230</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60283</t>
+          <t>59975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,0%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45497</t>
+          <t>45232</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>37749</t>
+          <t>38247</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>52736</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>45,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72941</t>
+          <t>73652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94730</t>
+          <t>94077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16479</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32427</t>
+          <t>32766</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3590</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8053</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>92933</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>119529</t>
+          <t>119254</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107728</t>
+          <t>107868</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>136017</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>208698</t>
+          <t>208006</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>248685</t>
+          <t>246483</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,49%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>128681</t>
+          <t>129014</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>156157</t>
+          <t>156781</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129166</t>
+          <t>129275</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>158250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>266985</t>
+          <t>265068</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>306529</t>
+          <t>306428</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,34%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55797</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>32799</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>52502</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73664</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101709</t>
+          <t>101649</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7446,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12991</t>
+          <t>12667</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3213</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido/a por sus padres en 2016 (tasa de respuesta: 93,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23707</t>
+          <t>24483</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19375</t>
+          <t>19890</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33730</t>
+          <t>32997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>47060</t>
+          <t>46919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66974</t>
+          <t>67226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,13%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>20432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34158</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23684</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37554</t>
+          <t>37882</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48173</t>
+          <t>47682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68444</t>
+          <t>68604</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15244</t>
+          <t>14863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>12978</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26989</t>
+          <t>26493</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5740</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34457</t>
+          <t>33715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50451</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>37197</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52691</t>
+          <t>53637</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>74553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97597</t>
+          <t>98033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43771</t>
+          <t>44078</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35964</t>
+          <t>36102</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52006</t>
+          <t>51927</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>68944</t>
+          <t>68583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>91145</t>
+          <t>90997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>21275</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19827</t>
+          <t>19532</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35170</t>
+          <t>35445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5198</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>7183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>983</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22700</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35351</t>
+          <t>35640</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>26494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40957</t>
+          <t>41142</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52616</t>
+          <t>53065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72709</t>
+          <t>72445</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26670</t>
+          <t>26381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>39513</t>
+          <t>40201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>40153</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55492</t>
+          <t>56475</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75212</t>
+          <t>75193</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5363</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6923</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8744</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45296</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>29765</t>
+          <t>28904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45907</t>
+          <t>45135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62061</t>
+          <t>61930</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85420</t>
+          <t>86260</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>56114</t>
+          <t>56672</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36094</t>
+          <t>35327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51962</t>
+          <t>52214</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>79053</t>
+          <t>78699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>102258</t>
+          <t>104116</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28439</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>28773</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46417</t>
+          <t>47339</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>123103</t>
+          <t>122974</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>155197</t>
+          <t>152817</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>125441</t>
+          <t>126821</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>155944</t>
+          <t>156022</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>259339</t>
+          <t>257749</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>303280</t>
+          <t>300514</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>127944</t>
+          <t>128777</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158970</t>
+          <t>157467</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>135837</t>
+          <t>134131</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>165913</t>
+          <t>164874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>274137</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>313663</t>
+          <t>315800</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,56%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38583</t>
+          <t>37989</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32702</t>
+          <t>33792</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>53993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>79222</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>106847</t>
+          <t>107927</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1070</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6905</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10317</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11090</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
